--- a/src/idfhub/helpers/materials.xlsx
+++ b/src/idfhub/helpers/materials.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexandre.cuer\Documents\GitHub\ladybug_codes\src\idfhub\helpers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{324EC5D2-45AC-4ECF-BD64-A1419FC937C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFEC0626-5A04-4AAB-A406-A845EECBD0E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{ED7ED0CA-3D09-4439-9886-20D250F5F193}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{ED7ED0CA-3D09-4439-9886-20D250F5F193}"/>
   </bookViews>
   <sheets>
     <sheet name="window" sheetId="1" r:id="rId1"/>
+    <sheet name="opaque_materials" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="36">
   <si>
     <t>low-e</t>
   </si>
@@ -88,6 +89,63 @@
   </si>
   <si>
     <t>solar diffusing</t>
+  </si>
+  <si>
+    <t>generic roof membrane</t>
+  </si>
+  <si>
+    <t>MediumRough</t>
+  </si>
+  <si>
+    <t>roughness</t>
+  </si>
+  <si>
+    <t>thickness</t>
+  </si>
+  <si>
+    <t>conductivity W/m/K</t>
+  </si>
+  <si>
+    <t>density kg/m3</t>
+  </si>
+  <si>
+    <t>specific heat J/kg/K</t>
+  </si>
+  <si>
+    <t>thermal absorptance</t>
+  </si>
+  <si>
+    <t>solar absorptance</t>
+  </si>
+  <si>
+    <t>visible absorptance</t>
+  </si>
+  <si>
+    <t>Generic 50mm insulation</t>
+  </si>
+  <si>
+    <t>Generic LW concrete</t>
+  </si>
+  <si>
+    <t>Generic Ceiling Air gap</t>
+  </si>
+  <si>
+    <t>Smooth</t>
+  </si>
+  <si>
+    <t>Generic Acoustic Tile</t>
+  </si>
+  <si>
+    <t>mediumSmooth</t>
+  </si>
+  <si>
+    <t>Generic interior Celing</t>
+  </si>
+  <si>
+    <t>Generic interior floor</t>
+  </si>
+  <si>
+    <t>Bois</t>
   </si>
 </sst>
 </file>
@@ -144,10 +202,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -665,4 +726,263 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34AD6268-2FEA-4BB2-9F47-526D41282FBB}">
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="22.21875" customWidth="1"/>
+    <col min="2" max="2" width="20.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3">
+        <v>0.01</v>
+      </c>
+      <c r="C3">
+        <v>0.05</v>
+      </c>
+      <c r="D3">
+        <v>0.1</v>
+      </c>
+      <c r="E3">
+        <v>0.1</v>
+      </c>
+      <c r="F3">
+        <v>0.02</v>
+      </c>
+      <c r="H3">
+        <v>2.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4">
+        <v>0.16</v>
+      </c>
+      <c r="C4">
+        <v>0.03</v>
+      </c>
+      <c r="D4">
+        <v>0.53</v>
+      </c>
+      <c r="E4">
+        <v>0.55600000000000005</v>
+      </c>
+      <c r="F4">
+        <v>0.06</v>
+      </c>
+      <c r="H4">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5">
+        <v>1120</v>
+      </c>
+      <c r="C5">
+        <v>43</v>
+      </c>
+      <c r="D5">
+        <v>1280</v>
+      </c>
+      <c r="E5">
+        <v>1.28</v>
+      </c>
+      <c r="F5">
+        <v>368</v>
+      </c>
+      <c r="H5">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6">
+        <v>1460</v>
+      </c>
+      <c r="C6">
+        <v>1210</v>
+      </c>
+      <c r="D6">
+        <v>840</v>
+      </c>
+      <c r="E6">
+        <v>1000</v>
+      </c>
+      <c r="F6">
+        <v>590</v>
+      </c>
+      <c r="H6">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7">
+        <v>0.9</v>
+      </c>
+      <c r="C7">
+        <v>0.9</v>
+      </c>
+      <c r="D7">
+        <v>0.9</v>
+      </c>
+      <c r="E7">
+        <v>0.9</v>
+      </c>
+      <c r="F7">
+        <v>0.9</v>
+      </c>
+      <c r="H7">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8">
+        <v>0.65</v>
+      </c>
+      <c r="C8">
+        <v>0.7</v>
+      </c>
+      <c r="D8">
+        <v>0.8</v>
+      </c>
+      <c r="E8">
+        <v>0.7</v>
+      </c>
+      <c r="F8">
+        <v>0.2</v>
+      </c>
+      <c r="H8">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9">
+        <v>0.65</v>
+      </c>
+      <c r="C9">
+        <v>0.7</v>
+      </c>
+      <c r="D9">
+        <v>0.8</v>
+      </c>
+      <c r="E9">
+        <v>0.7</v>
+      </c>
+      <c r="F9">
+        <v>0.2</v>
+      </c>
+      <c r="H9">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>